--- a/class_template.xlsx
+++ b/class_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="004F46E5"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <i val="1"/>
@@ -43,10 +43,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="004F46E5"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -64,8 +68,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FDF4"/>
-        <bgColor rgb="00F0FDF4"/>
+        <fgColor rgb="00EEF2FF"/>
+        <bgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,10 +99,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,11 +468,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -480,14 +484,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KKHMS Alathiyur - Class Data Entry Template</t>
+          <t>KKHMS Alathiyur - Class Data Entry (Division-wise Teacher Assignment)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fill in the data below. Each row = one class. Upload this file in the app to create classes in bulk.</t>
+          <t>Each row = one DIVISION. Fill Class, Division, Block, Type, Class Teacher, then subjects with teacher &amp; periods.</t>
         </is>
       </c>
     </row>
@@ -499,7 +503,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Divisions</t>
+          <t>Division</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -541,7 +545,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>A, B, C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -554,11 +558,7 @@
           <t>Arabic</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Teacher Name</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>First Language</t>
@@ -568,567 +568,2265 @@
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Malayalam II</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Maths</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Social Science</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="n">
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Work Education</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="n">
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr"/>
+      <c r="H87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr"/>
+      <c r="H88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>--- Class 9 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>A, B, C</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Block A</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>First Language</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>Malayalam II</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>Maths</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t>Social Science</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="inlineStr">
         <is>
           <t>PET</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>Work Education</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n"/>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n"/>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n"/>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n"/>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n"/>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n"/>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n"/>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n"/>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Work Education</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr"/>
+      <c r="H139" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>--- Class 10 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>A, B</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>Block B</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>First Language</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="G142" s="4" t="inlineStr"/>
+      <c r="H142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t>Malayalam II</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr"/>
+      <c r="H144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n"/>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="G145" s="5" t="inlineStr"/>
+      <c r="H145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n"/>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="inlineStr">
         <is>
           <t>Maths</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="G146" s="5" t="inlineStr"/>
+      <c r="H146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n"/>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="inlineStr">
         <is>
           <t>Social Science</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="G147" s="5" t="inlineStr"/>
+      <c r="H147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr"/>
+      <c r="H148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n"/>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr"/>
+      <c r="H149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr"/>
+      <c r="H150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr"/>
+      <c r="H151" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>First Language</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n"/>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="n"/>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Malayalam II</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr"/>
+      <c r="H155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr"/>
+      <c r="H156" s="5" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n"/>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n"/>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Social Science</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr"/>
+      <c r="H158" s="5" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1140,10 +2838,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1159,135 +2857,232 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Each CLASS starts on the row where Column A (Class) has a value (8, 9, or 10)</t>
+          <t>STRUCTURE: Each ROW is one subject for one division.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Column B (Divisions): Enter division letters separated by commas (e.g., A, B, C)</t>
+          <t>A new division starts whenever Column A (Class) AND Column B (Division) have values.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. Column C (Block): Enter the block name exactly as created in the app</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. Column D (Type): Arabic, Malayalam, Urdu/Sanskrit, Sanskrit/Urdu/Arabic, etc.</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>COLUMNS:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Column E (Class Teacher): Enter teacher name exactly as in the app</t>
+          <t xml:space="preserve">  A - Class: 8, 9, or 10 (fill only on first subject row of each division)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. Column F (Subject): Pre-filled. Do not change.</t>
+          <t xml:space="preserve">  B - Division: A, B, C, D... (fill only on first subject row of each division)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7. Column G (Teacher): Enter the teacher name who teaches this subject for this class</t>
+          <t xml:space="preserve">  C - Block: Block name as in app (fill only on first row of each division)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8. Column H (Periods/Week): Enter number of periods per week for each subject</t>
+          <t xml:space="preserve">  D - Type: Arabic/Malayalam/etc. (fill only on first row of each division)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E - Class Teacher: Teacher name (fill only on first row of each division)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>RULES:</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  F - Subject: Pre-filled subject name</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Total periods per class MUST equal 35 (5 days × 7 periods)</t>
+          <t xml:space="preserve">  G - Teacher: The teacher who teaches THIS subject to THIS division</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- PET, Music, Work Education, Art are fixed at 1 period/week (Class 8 &amp; 9 only)</t>
+          <t xml:space="preserve">  H - Periods/Week: Number of periods per week</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- Class 10 does NOT have PET, Music, WE, Art</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- Teacher names must match exactly with the names in the Teachers list</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE:</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Class | Div | Block   | Type   | CT     | Subject    | Teacher      | Periods</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>TYPES AVAILABLE:</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8     | A   | Block A | Arabic | Salma  | English    | Suresh Kumar | 5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Arabic, Malayalam, Urdu/Sanskrit, Sanskrit/Urdu/Arabic,</t>
+          <t xml:space="preserve">        |     |         |        |        | Maths      | Priya R      | 5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Malayalam/Arabic, Sanskrit/Arabic/Urdu/Malayalam, Sanskrit/Arabic,</t>
+          <t xml:space="preserve">        |     |         |        |        | Hindi      | Fathima N    | 4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Urdu/Arabic, Sanskrit, Urdu</t>
+          <t xml:space="preserve">  8     | B   | Block A | Arabic | Noor   | English    | Divya M      | 5</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        |     |         |        |        | Maths      | Rajesh M     | 5</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>After filling, upload this file in the app using the 'Upload Excel' button on the Classes page.</t>
+          <t xml:space="preserve">        |     |         |        |        | Hindi      | Fathima N    | 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>RULES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Total periods per division MUST equal 35 (5 days × 7 periods)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- PET, Music, Work Education, Art: fixed at 1 period/week (Class 8 &amp; 9 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Class 10 does NOT have PET, Music, WE, Art</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Teacher names must EXACTLY match names in the Teachers list</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>- You can have different teachers for same subject in different divisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>- Add/remove division rows as needed (copy a set of subject rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>TYPES AVAILABLE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Arabic, Malayalam, Urdu/Sanskrit, Sanskrit/Urdu/Arabic,</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Malayalam/Arabic, Sanskrit/Arabic/Urdu/Malayalam, Sanskrit/Arabic,</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Urdu/Arabic, Sanskrit, Urdu</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>After filling, upload this file in the app: Classes page → 'Upload Excel' button.</t>
         </is>
       </c>
     </row>

--- a/class_template.xlsx
+++ b/class_template.xlsx
@@ -495,6 +495,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -757,6 +758,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -977,6 +979,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -1197,6 +1200,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -1417,6 +1421,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
@@ -1637,6 +1642,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
@@ -1857,6 +1863,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
@@ -2080,6 +2087,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
@@ -2296,6 +2304,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="125"/>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
@@ -2512,6 +2521,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="140"/>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
@@ -2671,6 +2681,7 @@
       <c r="G151" s="5" t="inlineStr"/>
       <c r="H151" s="5" t="inlineStr"/>
     </row>
+    <row r="152"/>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
@@ -2851,9 +2862,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2868,9 +2877,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -2934,9 +2941,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -2993,9 +2998,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
@@ -3045,9 +3048,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
@@ -3076,9 +3077,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
